--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="330" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{92348CEB-612A-4280-B9D2-44D395832B09}"/>
+  <xr:revisionPtr revIDLastSave="331" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD3CB67-D860-42D6-BB92-65A755714461}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="157">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="156">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -399,9 +399,6 @@
   </si>
   <si>
     <t>HP 10K - VENDA</t>
-  </si>
-  <si>
-    <t>HP 75500 - VENDA</t>
   </si>
   <si>
     <t>HP WS6600 - CAREPACK</t>
@@ -928,7 +925,7 @@
         <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -976,10 +973,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>147</v>
+      </c>
+      <c r="C10" t="s">
         <v>148</v>
-      </c>
-      <c r="C10" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1009,10 +1006,10 @@
         <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D13" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1020,7 +1017,7 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1066,7 +1063,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
@@ -1188,7 +1185,7 @@
         <v>121</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1212,7 +1209,7 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C35" t="s">
         <v>98</v>
@@ -1223,10 +1220,10 @@
         <v>31</v>
       </c>
       <c r="B36" t="s">
+        <v>123</v>
+      </c>
+      <c r="C36" t="s">
         <v>124</v>
-      </c>
-      <c r="C36" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -1234,7 +1231,7 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -1267,7 +1264,7 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
         <v>96</v>
@@ -1278,7 +1275,7 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -1286,10 +1283,10 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="C42" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -1297,7 +1294,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -1305,7 +1302,7 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -1321,7 +1318,7 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -1329,7 +1326,7 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C47" t="s">
         <v>102</v>
@@ -1340,7 +1337,7 @@
         <v>94</v>
       </c>
       <c r="B48" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -1351,7 +1348,7 @@
         <v>119</v>
       </c>
       <c r="C49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -1359,7 +1356,7 @@
         <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -1375,10 +1372,10 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C52" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -1394,7 +1391,7 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -1402,7 +1399,7 @@
         <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -1418,7 +1415,7 @@
         <v>95</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -1426,7 +1423,7 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -1439,10 +1436,10 @@
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>144</v>
+      </c>
+      <c r="B60" t="s">
         <v>145</v>
-      </c>
-      <c r="B60" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -1450,10 +1447,10 @@
         <v>54</v>
       </c>
       <c r="B61" t="s">
+        <v>133</v>
+      </c>
+      <c r="C61" t="s">
         <v>134</v>
-      </c>
-      <c r="C61" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -1461,7 +1458,7 @@
         <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -1469,10 +1466,10 @@
         <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C63" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -1480,7 +1477,7 @@
         <v>57</v>
       </c>
       <c r="B64" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -1488,7 +1485,7 @@
         <v>58</v>
       </c>
       <c r="B65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -1520,7 +1517,7 @@
         <v>60</v>
       </c>
       <c r="B69" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -1528,7 +1525,7 @@
         <v>61</v>
       </c>
       <c r="B70" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -1536,7 +1533,7 @@
         <v>62</v>
       </c>
       <c r="B71" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -1544,7 +1541,7 @@
         <v>63</v>
       </c>
       <c r="B72" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -1552,7 +1549,7 @@
         <v>64</v>
       </c>
       <c r="B73" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="C73" t="s">
         <v>121</v>
@@ -1563,7 +1560,7 @@
         <v>65</v>
       </c>
       <c r="B74" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
@@ -1579,7 +1576,7 @@
         <v>67</v>
       </c>
       <c r="B76" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
@@ -1587,7 +1584,7 @@
         <v>68</v>
       </c>
       <c r="B77" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
@@ -1595,10 +1592,10 @@
         <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C78" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -1606,7 +1603,7 @@
         <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C79" t="s">
         <v>110</v>
@@ -1617,10 +1614,10 @@
         <v>71</v>
       </c>
       <c r="B80" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="C80" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.35">
@@ -1628,7 +1625,7 @@
         <v>72</v>
       </c>
       <c r="B81" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.35">
@@ -1636,7 +1633,7 @@
         <v>73</v>
       </c>
       <c r="B82" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.35">
@@ -1666,7 +1663,7 @@
         <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.35">
@@ -1682,7 +1679,7 @@
         <v>78</v>
       </c>
       <c r="B87" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.35">
@@ -1690,7 +1687,7 @@
         <v>79</v>
       </c>
       <c r="B88" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.35">
@@ -1698,7 +1695,7 @@
         <v>80</v>
       </c>
       <c r="B89" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.35">
@@ -1706,7 +1703,7 @@
         <v>81</v>
       </c>
       <c r="B90" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.35">
@@ -1714,7 +1711,7 @@
         <v>82</v>
       </c>
       <c r="B91" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.35">
@@ -1722,7 +1719,7 @@
         <v>83</v>
       </c>
       <c r="B92" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.35">
@@ -1730,7 +1727,7 @@
         <v>84</v>
       </c>
       <c r="B93" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
   </sheetData>

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="331" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCD3CB67-D860-42D6-BB92-65A755714461}"/>
+  <xr:revisionPtr revIDLastSave="334" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AEDA7CF-8C90-4344-8BA0-E69A7A7467C3}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="156">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="158">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -501,6 +501,12 @@
   </si>
   <si>
     <t>HP W7250 - VENDA</t>
+  </si>
+  <si>
+    <t>BRADY CORP</t>
+  </si>
+  <si>
+    <t>ABG - VENDA</t>
   </si>
 </sst>
 </file>
@@ -868,14 +874,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F93"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:F94"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="23.1796875" customWidth="1"/>
-    <col min="2" max="6" width="25.54296875" customWidth="1"/>
+    <col min="1" max="1" width="23.140625" customWidth="1"/>
+    <col min="2" max="6" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -895,7 +901,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -903,7 +909,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -917,7 +923,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -928,7 +934,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -936,7 +942,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -944,7 +950,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -952,7 +958,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -960,7 +966,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -968,7 +974,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -979,7 +985,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -987,7 +993,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -998,7 +1004,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1012,7 +1018,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1020,7 +1026,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1031,7 +1037,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1039,7 +1045,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1047,7 +1053,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1058,7 +1064,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1066,7 +1072,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1074,7 +1080,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1085,7 +1091,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -1093,7 +1099,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1101,7 +1107,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1109,7 +1115,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -1123,7 +1129,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -1134,7 +1140,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>93</v>
       </c>
@@ -1142,7 +1148,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -1150,7 +1156,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -1158,7 +1164,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1169,7 +1175,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1177,7 +1183,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1188,7 +1194,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1196,7 +1202,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1204,7 +1210,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -1215,7 +1221,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -1226,7 +1232,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -1234,7 +1240,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -1245,7 +1251,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -1259,7 +1265,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>36</v>
       </c>
@@ -1270,7 +1276,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -1278,7 +1284,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -1289,7 +1295,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -1297,7 +1303,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -1305,7 +1311,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>41</v>
       </c>
@@ -1313,7 +1319,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>42</v>
       </c>
@@ -1321,7 +1327,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -1332,7 +1338,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -1340,7 +1346,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>44</v>
       </c>
@@ -1351,7 +1357,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>45</v>
       </c>
@@ -1359,7 +1365,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>46</v>
       </c>
@@ -1367,7 +1373,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>47</v>
       </c>
@@ -1378,7 +1384,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1386,7 +1392,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -1394,7 +1400,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1402,7 +1408,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>51</v>
       </c>
@@ -1410,7 +1416,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>95</v>
       </c>
@@ -1418,7 +1424,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>52</v>
       </c>
@@ -1426,7 +1432,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>53</v>
       </c>
@@ -1434,7 +1440,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>144</v>
       </c>
@@ -1442,7 +1448,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -1453,7 +1459,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -1461,7 +1467,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>56</v>
       </c>
@@ -1472,7 +1478,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -1480,7 +1486,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>58</v>
       </c>
@@ -1488,7 +1494,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>91</v>
       </c>
@@ -1496,7 +1502,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -1504,7 +1510,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>59</v>
       </c>
@@ -1512,7 +1518,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>60</v>
       </c>
@@ -1520,7 +1526,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>61</v>
       </c>
@@ -1528,7 +1534,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>62</v>
       </c>
@@ -1536,7 +1542,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>63</v>
       </c>
@@ -1544,7 +1550,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>64</v>
       </c>
@@ -1555,7 +1561,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>65</v>
       </c>
@@ -1563,7 +1569,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>66</v>
       </c>
@@ -1571,7 +1577,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>67</v>
       </c>
@@ -1579,7 +1585,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>68</v>
       </c>
@@ -1587,7 +1593,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>69</v>
       </c>
@@ -1598,7 +1604,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>70</v>
       </c>
@@ -1609,7 +1615,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>71</v>
       </c>
@@ -1620,7 +1626,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>72</v>
       </c>
@@ -1628,7 +1634,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>73</v>
       </c>
@@ -1636,7 +1642,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>74</v>
       </c>
@@ -1644,7 +1650,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -1658,7 +1664,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>76</v>
       </c>
@@ -1666,7 +1672,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>77</v>
       </c>
@@ -1674,7 +1680,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>78</v>
       </c>
@@ -1682,7 +1688,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>79</v>
       </c>
@@ -1690,7 +1696,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>80</v>
       </c>
@@ -1698,7 +1704,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>81</v>
       </c>
@@ -1706,7 +1712,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -1714,7 +1720,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -1722,12 +1728,20 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>84</v>
       </c>
       <c r="B93" t="s">
         <v>126</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>156</v>
+      </c>
+      <c r="B94" t="s">
+        <v>157</v>
       </c>
     </row>
   </sheetData>

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="334" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4AEDA7CF-8C90-4344-8BA0-E69A7A7467C3}"/>
+  <xr:revisionPtr revIDLastSave="336" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757EDFDA-6AE6-42A9-9628-B1FAE33F0A9C}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="158">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="160">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -507,6 +507,12 @@
   </si>
   <si>
     <t>ABG - VENDA</t>
+  </si>
+  <si>
+    <t>TECNOPRINT</t>
+  </si>
+  <si>
+    <t>ABG Ti200 - VENDA</t>
   </si>
 </sst>
 </file>
@@ -874,7 +880,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F94"/>
+  <dimension ref="A1:F95"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="23.140625" customWidth="1"/>
@@ -1744,6 +1750,14 @@
         <v>157</v>
       </c>
     </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>158</v>
+      </c>
+      <c r="B95" t="s">
+        <v>159</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="336" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{757EDFDA-6AE6-42A9-9628-B1FAE33F0A9C}"/>
+  <xr:revisionPtr revIDLastSave="337" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1005F7F-8A94-4540-AE6B-7C95C4BD8E9D}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="227" uniqueCount="160">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="161">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -513,6 +513,9 @@
   </si>
   <si>
     <t>ABG Ti200 - VENDA</t>
+  </si>
+  <si>
+    <t>ABG DS3 - VENDA</t>
   </si>
 </sst>
 </file>
@@ -1096,6 +1099,9 @@
       <c r="C21" t="s">
         <v>96</v>
       </c>
+      <c r="D21" t="s">
+        <v>160</v>
+      </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A22" t="s">

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="337" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E1005F7F-8A94-4540-AE6B-7C95C4BD8E9D}"/>
+  <xr:revisionPtr revIDLastSave="339" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E05A0BF-C769-4817-B2D3-25222AC3E4C5}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="161">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -884,13 +884,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F95"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="23.140625" customWidth="1"/>
-    <col min="2" max="6" width="25.5703125" customWidth="1"/>
+    <col min="1" max="1" width="23.1796875" customWidth="1"/>
+    <col min="2" max="6" width="25.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -910,7 +910,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
         <v>1</v>
       </c>
@@ -918,7 +918,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -932,7 +932,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
         <v>3</v>
       </c>
@@ -943,7 +943,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
         <v>4</v>
       </c>
@@ -951,7 +951,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
         <v>5</v>
       </c>
@@ -959,7 +959,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -967,7 +967,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
         <v>7</v>
       </c>
@@ -975,7 +975,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
         <v>92</v>
       </c>
@@ -983,7 +983,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
         <v>8</v>
       </c>
@@ -994,7 +994,7 @@
         <v>148</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
         <v>9</v>
       </c>
@@ -1002,7 +1002,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -1013,7 +1013,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
         <v>11</v>
       </c>
@@ -1027,7 +1027,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
         <v>35</v>
       </c>
@@ -1035,7 +1035,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
         <v>12</v>
       </c>
@@ -1046,7 +1046,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
         <v>13</v>
       </c>
@@ -1054,7 +1054,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
         <v>14</v>
       </c>
@@ -1062,7 +1062,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
         <v>15</v>
       </c>
@@ -1073,7 +1073,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
         <v>16</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
         <v>17</v>
       </c>
@@ -1089,7 +1089,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -1103,7 +1103,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
         <v>90</v>
       </c>
@@ -1111,7 +1111,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
         <v>19</v>
       </c>
@@ -1119,7 +1119,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
         <v>20</v>
       </c>
@@ -1127,7 +1127,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
         <v>21</v>
       </c>
@@ -1140,8 +1140,11 @@
       <c r="D25" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E25" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -1152,7 +1155,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
         <v>93</v>
       </c>
@@ -1160,7 +1163,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
         <v>23</v>
       </c>
@@ -1168,7 +1171,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
         <v>24</v>
       </c>
@@ -1176,7 +1179,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
         <v>25</v>
       </c>
@@ -1187,7 +1190,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
         <v>26</v>
       </c>
@@ -1195,7 +1198,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
         <v>27</v>
       </c>
@@ -1206,7 +1209,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
         <v>28</v>
       </c>
@@ -1214,7 +1217,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
         <v>29</v>
       </c>
@@ -1222,7 +1225,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
         <v>30</v>
       </c>
@@ -1233,7 +1236,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
         <v>31</v>
       </c>
@@ -1244,7 +1247,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
         <v>32</v>
       </c>
@@ -1252,7 +1255,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
         <v>33</v>
       </c>
@@ -1263,7 +1266,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
         <v>34</v>
       </c>
@@ -1277,7 +1280,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
         <v>36</v>
       </c>
@@ -1288,7 +1291,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
         <v>37</v>
       </c>
@@ -1296,7 +1299,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
         <v>38</v>
       </c>
@@ -1307,7 +1310,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
         <v>39</v>
       </c>
@@ -1315,7 +1318,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
         <v>40</v>
       </c>
@@ -1323,7 +1326,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
         <v>41</v>
       </c>
@@ -1331,7 +1334,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
         <v>42</v>
       </c>
@@ -1339,7 +1342,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
         <v>43</v>
       </c>
@@ -1350,7 +1353,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
         <v>94</v>
       </c>
@@ -1358,7 +1361,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
         <v>44</v>
       </c>
@@ -1369,7 +1372,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
         <v>45</v>
       </c>
@@ -1377,7 +1380,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
         <v>46</v>
       </c>
@@ -1385,7 +1388,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
         <v>47</v>
       </c>
@@ -1396,7 +1399,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
         <v>48</v>
       </c>
@@ -1404,7 +1407,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
         <v>49</v>
       </c>
@@ -1412,7 +1415,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
         <v>50</v>
       </c>
@@ -1420,7 +1423,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
         <v>51</v>
       </c>
@@ -1428,7 +1431,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
         <v>95</v>
       </c>
@@ -1436,7 +1439,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
         <v>52</v>
       </c>
@@ -1444,7 +1447,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
         <v>53</v>
       </c>
@@ -1452,7 +1455,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
         <v>144</v>
       </c>
@@ -1460,7 +1463,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
         <v>54</v>
       </c>
@@ -1471,7 +1474,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
         <v>55</v>
       </c>
@@ -1479,7 +1482,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
         <v>56</v>
       </c>
@@ -1490,7 +1493,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
         <v>57</v>
       </c>
@@ -1498,7 +1501,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A65" t="s">
         <v>58</v>
       </c>
@@ -1506,7 +1509,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A66" t="s">
         <v>91</v>
       </c>
@@ -1514,7 +1517,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A67" t="s">
         <v>19</v>
       </c>
@@ -1522,7 +1525,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A68" t="s">
         <v>59</v>
       </c>
@@ -1530,7 +1533,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A69" t="s">
         <v>60</v>
       </c>
@@ -1538,7 +1541,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A70" t="s">
         <v>61</v>
       </c>
@@ -1546,7 +1549,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A71" t="s">
         <v>62</v>
       </c>
@@ -1554,7 +1557,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A72" t="s">
         <v>63</v>
       </c>
@@ -1562,7 +1565,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A73" t="s">
         <v>64</v>
       </c>
@@ -1573,7 +1576,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A74" t="s">
         <v>65</v>
       </c>
@@ -1581,7 +1584,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A75" t="s">
         <v>66</v>
       </c>
@@ -1589,7 +1592,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A76" t="s">
         <v>67</v>
       </c>
@@ -1597,7 +1600,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A77" t="s">
         <v>68</v>
       </c>
@@ -1605,7 +1608,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A78" t="s">
         <v>69</v>
       </c>
@@ -1616,7 +1619,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A79" t="s">
         <v>70</v>
       </c>
@@ -1627,7 +1630,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A80" t="s">
         <v>71</v>
       </c>
@@ -1638,7 +1641,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>72</v>
       </c>
@@ -1646,7 +1649,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>73</v>
       </c>
@@ -1654,7 +1657,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>74</v>
       </c>
@@ -1662,7 +1665,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -1676,7 +1679,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>76</v>
       </c>
@@ -1684,7 +1687,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>77</v>
       </c>
@@ -1692,7 +1695,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>78</v>
       </c>
@@ -1700,7 +1703,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>79</v>
       </c>
@@ -1708,7 +1711,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>80</v>
       </c>
@@ -1716,7 +1719,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>81</v>
       </c>
@@ -1724,7 +1727,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -1732,7 +1735,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -1740,7 +1743,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>84</v>
       </c>
@@ -1748,7 +1751,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>156</v>
       </c>
@@ -1756,7 +1759,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>158</v>
       </c>

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="339" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6E05A0BF-C769-4817-B2D3-25222AC3E4C5}"/>
+  <xr:revisionPtr revIDLastSave="340" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7EF1D17-8860-4C4E-99CF-44E04B5B793D}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="161">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -1641,7 +1641,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="81" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A81" t="s">
         <v>72</v>
       </c>
@@ -1649,7 +1649,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="82" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A82" t="s">
         <v>73</v>
       </c>
@@ -1657,7 +1657,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="83" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A83" t="s">
         <v>74</v>
       </c>
@@ -1665,7 +1665,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="84" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A84" t="s">
         <v>75</v>
       </c>
@@ -1678,8 +1678,11 @@
       <c r="D84" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="85" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="E84" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="85" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A85" t="s">
         <v>76</v>
       </c>
@@ -1687,7 +1690,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="86" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A86" t="s">
         <v>77</v>
       </c>
@@ -1695,7 +1698,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="87" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A87" t="s">
         <v>78</v>
       </c>
@@ -1703,7 +1706,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="88" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A88" t="s">
         <v>79</v>
       </c>
@@ -1711,7 +1714,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="89" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A89" t="s">
         <v>80</v>
       </c>
@@ -1719,7 +1722,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="90" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>81</v>
       </c>
@@ -1727,7 +1730,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="91" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>82</v>
       </c>
@@ -1735,7 +1738,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="92" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -1743,7 +1746,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="93" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>84</v>
       </c>
@@ -1751,7 +1754,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="94" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>156</v>
       </c>
@@ -1759,7 +1762,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="95" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>158</v>
       </c>

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="340" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D7EF1D17-8860-4C4E-99CF-44E04B5B793D}"/>
+  <xr:revisionPtr revIDLastSave="342" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39462ADE-C498-4FA5-8D5D-D854CEDCC443}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="161">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="162">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -516,6 +516,9 @@
   </si>
   <si>
     <t>ABG DS3 - VENDA</t>
+  </si>
+  <si>
+    <t>DELPAK</t>
   </si>
 </sst>
 </file>
@@ -883,7 +886,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F95"/>
+  <dimension ref="A1:F96"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="23.1796875" customWidth="1"/>
@@ -1770,6 +1773,14 @@
         <v>159</v>
       </c>
     </row>
+    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A96" t="s">
+        <v>161</v>
+      </c>
+      <c r="B96" t="s">
+        <v>102</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="342" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{39462ADE-C498-4FA5-8D5D-D854CEDCC443}"/>
+  <xr:revisionPtr revIDLastSave="345" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAB4776E-3D9C-44A9-B7C0-AED5C489DD75}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="232" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="162">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -918,7 +918,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>96</v>
+        <v>103</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1152,9 +1152,6 @@
         <v>22</v>
       </c>
       <c r="B26" t="s">
-        <v>116</v>
-      </c>
-      <c r="C26" t="s">
         <v>117</v>
       </c>
     </row>

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="345" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FAB4776E-3D9C-44A9-B7C0-AED5C489DD75}"/>
+  <xr:revisionPtr revIDLastSave="346" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57692F32-7466-455C-8906-0FF2E2DA0673}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="163">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -519,6 +519,9 @@
   </si>
   <si>
     <t>DELPAK</t>
+  </si>
+  <si>
+    <t>HP 6K - NACIONALIZAÇÃO</t>
   </si>
 </sst>
 </file>
@@ -918,7 +921,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>103</v>
+        <v>162</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="346" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{57692F32-7466-455C-8906-0FF2E2DA0673}"/>
+  <xr:revisionPtr revIDLastSave="347" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4B3B488-30BD-4DD0-AA9C-58DCFF32BD76}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="162">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -495,9 +495,6 @@
   </si>
   <si>
     <t>HP INDIGO 12K - CAREPACK</t>
-  </si>
-  <si>
-    <t>HP 100K - VENDA</t>
   </si>
   <si>
     <t>HP W7250 - VENDA</t>
@@ -921,7 +918,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -1027,10 +1024,10 @@
         <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="D13" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1084,7 +1081,7 @@
         <v>16</v>
       </c>
       <c r="B19" t="s">
-        <v>154</v>
+        <v>112</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -1106,7 +1103,7 @@
         <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -1147,7 +1144,7 @@
         <v>96</v>
       </c>
       <c r="E25" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -1682,7 +1679,7 @@
         <v>100</v>
       </c>
       <c r="E84" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
@@ -1759,23 +1756,23 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
+        <v>155</v>
+      </c>
+      <c r="B94" t="s">
         <v>156</v>
-      </c>
-      <c r="B94" t="s">
-        <v>157</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
+        <v>157</v>
+      </c>
+      <c r="B95" t="s">
         <v>158</v>
-      </c>
-      <c r="B95" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="B96" t="s">
         <v>102</v>

--- a/data/clientes.xlsx
+++ b/data/clientes.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://maquinascomprint-my.sharepoint.com/personal/ricardo_almeida_comprint_com_br/Documents/PROJETOS/OUTROS/Programação/chatbot-whatsapp-estoque/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="347" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A4B3B488-30BD-4DD0-AA9C-58DCFF32BD76}"/>
+  <xr:revisionPtr revIDLastSave="348" documentId="11_FFC65FC0F879EECECE170B54ABAE8EF57AB2EA2D" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FD0D8C03-6FDB-4D0B-9652-BD291F40204E}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="162">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="231" uniqueCount="161">
   <si>
     <t>CLIENTE</t>
   </si>
@@ -387,9 +387,6 @@
   </si>
   <si>
     <t>HP INDIGO 18K - CIF</t>
-  </si>
-  <si>
-    <t>HP 15K - CIF</t>
   </si>
   <si>
     <t>HP 12K - CAREPACK</t>
@@ -918,7 +915,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.35">
@@ -943,7 +940,7 @@
         <v>97</v>
       </c>
       <c r="C4" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.35">
@@ -991,10 +988,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>146</v>
+      </c>
+      <c r="C10" t="s">
         <v>147</v>
-      </c>
-      <c r="C10" t="s">
-        <v>148</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.35">
@@ -1024,10 +1021,10 @@
         <v>108</v>
       </c>
       <c r="C13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="D13" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.35">
@@ -1035,7 +1032,7 @@
         <v>35</v>
       </c>
       <c r="B14" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.35">
@@ -1103,7 +1100,7 @@
         <v>96</v>
       </c>
       <c r="D21" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
@@ -1144,7 +1141,7 @@
         <v>96</v>
       </c>
       <c r="E25" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -1160,7 +1157,7 @@
         <v>93</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
@@ -1176,7 +1173,7 @@
         <v>24</v>
       </c>
       <c r="B29" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
@@ -1187,7 +1184,7 @@
         <v>103</v>
       </c>
       <c r="C30" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
@@ -1203,10 +1200,10 @@
         <v>27</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.35">
@@ -1230,7 +1227,7 @@
         <v>30</v>
       </c>
       <c r="B35" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="C35" t="s">
         <v>98</v>
@@ -1241,10 +1238,10 @@
         <v>31</v>
       </c>
       <c r="B36" t="s">
+        <v>122</v>
+      </c>
+      <c r="C36" t="s">
         <v>123</v>
-      </c>
-      <c r="C36" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.35">
@@ -1252,7 +1249,7 @@
         <v>32</v>
       </c>
       <c r="B37" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.35">
@@ -1285,7 +1282,7 @@
         <v>36</v>
       </c>
       <c r="B40" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C40" t="s">
         <v>96</v>
@@ -1296,7 +1293,7 @@
         <v>37</v>
       </c>
       <c r="B41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.35">
@@ -1304,10 +1301,10 @@
         <v>38</v>
       </c>
       <c r="B42" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C42" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.35">
@@ -1315,7 +1312,7 @@
         <v>39</v>
       </c>
       <c r="B43" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.35">
@@ -1323,7 +1320,7 @@
         <v>40</v>
       </c>
       <c r="B44" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.35">
@@ -1339,7 +1336,7 @@
         <v>42</v>
       </c>
       <c r="B46" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.35">
@@ -1347,7 +1344,7 @@
         <v>43</v>
       </c>
       <c r="B47" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="C47" t="s">
         <v>102</v>
@@ -1358,7 +1355,7 @@
         <v>94</v>
       </c>
       <c r="B48" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="49" spans="1:3" x14ac:dyDescent="0.35">
@@ -1366,10 +1363,10 @@
         <v>44</v>
       </c>
       <c r="B49" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="C49" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="50" spans="1:3" x14ac:dyDescent="0.35">
@@ -1377,7 +1374,7 @@
         <v>45</v>
       </c>
       <c r="B50" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="51" spans="1:3" x14ac:dyDescent="0.35">
@@ -1393,10 +1390,10 @@
         <v>47</v>
       </c>
       <c r="B52" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C52" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="53" spans="1:3" x14ac:dyDescent="0.35">
@@ -1412,7 +1409,7 @@
         <v>49</v>
       </c>
       <c r="B54" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="55" spans="1:3" x14ac:dyDescent="0.35">
@@ -1420,7 +1417,7 @@
         <v>50</v>
       </c>
       <c r="B55" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="56" spans="1:3" x14ac:dyDescent="0.35">
@@ -1436,7 +1433,7 @@
         <v>95</v>
       </c>
       <c r="B57" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="58" spans="1:3" x14ac:dyDescent="0.35">
@@ -1444,7 +1441,7 @@
         <v>52</v>
       </c>
       <c r="B58" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="59" spans="1:3" x14ac:dyDescent="0.35">
@@ -1452,15 +1449,15 @@
         <v>53</v>
       </c>
       <c r="B59" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="60" spans="1:3" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
+        <v>143</v>
+      </c>
+      <c r="B60" t="s">
         <v>144</v>
-      </c>
-      <c r="B60" t="s">
-        <v>145</v>
       </c>
     </row>
     <row r="61" spans="1:3" x14ac:dyDescent="0.35">
@@ -1468,10 +1465,10 @@
         <v>54</v>
       </c>
       <c r="B61" t="s">
+        <v>132</v>
+      </c>
+      <c r="C61" t="s">
         <v>133</v>
-      </c>
-      <c r="C61" t="s">
-        <v>134</v>
       </c>
     </row>
     <row r="62" spans="1:3" x14ac:dyDescent="0.35">
@@ -1479,7 +1476,7 @@
         <v>55</v>
       </c>
       <c r="B62" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
     </row>
     <row r="63" spans="1:3" x14ac:dyDescent="0.35">
@@ -1487,10 +1484,10 @@
         <v>56</v>
       </c>
       <c r="B63" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="C63" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="64" spans="1:3" x14ac:dyDescent="0.35">
@@ -1498,7 +1495,7 @@
         <v>57</v>
       </c>
       <c r="B64" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="65" spans="1:3" x14ac:dyDescent="0.35">
@@ -1506,7 +1503,7 @@
         <v>58</v>
       </c>
       <c r="B65" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="66" spans="1:3" x14ac:dyDescent="0.35">
@@ -1530,7 +1527,7 @@
         <v>59</v>
       </c>
       <c r="B68" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.35">
@@ -1538,7 +1535,7 @@
         <v>60</v>
       </c>
       <c r="B69" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.35">
@@ -1546,7 +1543,7 @@
         <v>61</v>
       </c>
       <c r="B70" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.35">
@@ -1554,7 +1551,7 @@
         <v>62</v>
       </c>
       <c r="B71" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.35">
@@ -1562,7 +1559,7 @@
         <v>63</v>
       </c>
       <c r="B72" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.35">
@@ -1570,10 +1567,10 @@
         <v>64</v>
       </c>
       <c r="B73" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="C73" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.35">
@@ -1581,7 +1578,7 @@
         <v>65</v>
       </c>
       <c r="B74" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.35">
@@ -1597,7 +1594,7 @@
         <v>67</v>
       </c>
       <c r="B76" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.35">
@@ -1605,7 +1602,7 @@
         <v>68</v>
       </c>
       <c r="B77" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.35">
@@ -1613,10 +1610,10 @@
         <v>69</v>
       </c>
       <c r="B78" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C78" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.35">
@@ -1624,7 +1621,7 @@
         <v>70</v>
       </c>
       <c r="B79" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="C79" t="s">
         <v>110</v>
@@ -1635,10 +1632,10 @@
         <v>71</v>
       </c>
       <c r="B80" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="C80" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.35">
@@ -1646,7 +1643,7 @@
         <v>72</v>
       </c>
       <c r="B81" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.35">
@@ -1654,7 +1651,7 @@
         <v>73</v>
       </c>
       <c r="B82" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.35">
@@ -1670,7 +1667,7 @@
         <v>75</v>
       </c>
       <c r="B84" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C84" t="s">
         <v>100</v>
@@ -1679,7 +1676,7 @@
         <v>100</v>
       </c>
       <c r="E84" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.35">
@@ -1687,7 +1684,7 @@
         <v>76</v>
       </c>
       <c r="B85" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
@@ -1703,7 +1700,7 @@
         <v>78</v>
       </c>
       <c r="B87" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
@@ -1711,7 +1708,7 @@
         <v>79</v>
       </c>
       <c r="B88" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
@@ -1719,7 +1716,7 @@
         <v>80</v>
       </c>
       <c r="B89" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.35">
@@ -1727,7 +1724,7 @@
         <v>81</v>
       </c>
       <c r="B90" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.35">
@@ -1735,7 +1732,7 @@
         <v>82</v>
       </c>
       <c r="B91" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.35">
@@ -1743,7 +1740,7 @@
         <v>83</v>
       </c>
       <c r="B92" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
@@ -1751,28 +1748,28 @@
         <v>84</v>
       </c>
       <c r="B93" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
+        <v>154</v>
+      </c>
+      <c r="B94" t="s">
         <v>155</v>
-      </c>
-      <c r="B94" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
+        <v>156</v>
+      </c>
+      <c r="B95" t="s">
         <v>157</v>
-      </c>
-      <c r="B95" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="B96" t="s">
         <v>102</v>
